--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,566 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124756711</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>453779</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6991289</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124756714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>453714</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6991389</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124756712</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91410</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>453753</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6991387</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124756713</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>453753</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6991387</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124753575</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Häggsåsen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>453767</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6991316</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124709059</v>
+        <v>124709483</v>
       </c>
       <c r="B2" t="n">
-        <v>74824</v>
+        <v>91579</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1460</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453778</v>
+        <v>453754</v>
       </c>
       <c r="R2" t="n">
-        <v>6991352</v>
+        <v>6991313</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124709483</v>
+        <v>124709059</v>
       </c>
       <c r="B3" t="n">
-        <v>91579</v>
+        <v>74824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>1460</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453754</v>
+        <v>453778</v>
       </c>
       <c r="R3" t="n">
-        <v>6991313</v>
+        <v>6991352</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124756712</v>
+        <v>124753575</v>
       </c>
       <c r="B6" t="n">
-        <v>91410</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,29 +1134,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453753</v>
+        <v>453767</v>
       </c>
       <c r="R6" t="n">
-        <v>6991387</v>
+        <v>6991316</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,19 +1191,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,22 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124756713</v>
+        <v>124756712</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1236,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1337,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124753575</v>
+        <v>124756713</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1373,14 +1363,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453767</v>
+        <v>453753</v>
       </c>
       <c r="R8" t="n">
-        <v>6991316</v>
+        <v>6991387</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,9 +1400,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,12 +1427,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124709483</v>
+        <v>124709059</v>
       </c>
       <c r="B2" t="n">
-        <v>91579</v>
+        <v>74824</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>1460</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453754</v>
+        <v>453778</v>
       </c>
       <c r="R2" t="n">
-        <v>6991313</v>
+        <v>6991352</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124709059</v>
+        <v>124709483</v>
       </c>
       <c r="B3" t="n">
-        <v>74824</v>
+        <v>91579</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1460</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453778</v>
+        <v>453754</v>
       </c>
       <c r="R3" t="n">
-        <v>6991352</v>
+        <v>6991313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756711</v>
+        <v>124756713</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453779</v>
+        <v>453753</v>
       </c>
       <c r="R4" t="n">
-        <v>6991289</v>
+        <v>6991387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,21 +975,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124756714</v>
+        <v>124756712</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91410</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1007,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453714</v>
+        <v>453753</v>
       </c>
       <c r="R5" t="n">
-        <v>6991389</v>
+        <v>6991387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1220,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124756712</v>
+        <v>124756714</v>
       </c>
       <c r="B7" t="n">
-        <v>91410</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,16 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453753</v>
+        <v>453714</v>
       </c>
       <c r="R7" t="n">
-        <v>6991387</v>
+        <v>6991389</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1275,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1285,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124756713</v>
+        <v>124756711</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453753</v>
+        <v>453779</v>
       </c>
       <c r="R8" t="n">
-        <v>6991387</v>
+        <v>6991289</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,6 +1408,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124709059</v>
+        <v>124709483</v>
       </c>
       <c r="B2" t="n">
-        <v>74824</v>
+        <v>91579</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1460</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453778</v>
+        <v>453754</v>
       </c>
       <c r="R2" t="n">
-        <v>6991352</v>
+        <v>6991313</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124709483</v>
+        <v>124709059</v>
       </c>
       <c r="B3" t="n">
-        <v>91579</v>
+        <v>74824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>1460</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453754</v>
+        <v>453778</v>
       </c>
       <c r="R3" t="n">
-        <v>6991313</v>
+        <v>6991352</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124756712</v>
+        <v>124756711</v>
       </c>
       <c r="B5" t="n">
-        <v>91410</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,16 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453753</v>
+        <v>453779</v>
       </c>
       <c r="R5" t="n">
-        <v>6991387</v>
+        <v>6991289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,6 +1087,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1098,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124753575</v>
+        <v>124756714</v>
       </c>
       <c r="B6" t="n">
         <v>91012</v>
@@ -1134,14 +1154,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453767</v>
+        <v>453714</v>
       </c>
       <c r="R6" t="n">
-        <v>6991316</v>
+        <v>6991389</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,9 +1191,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,22 +1218,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124756714</v>
+        <v>124756712</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1246,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453714</v>
+        <v>453753</v>
       </c>
       <c r="R7" t="n">
-        <v>6991389</v>
+        <v>6991387</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124756711</v>
+        <v>124753575</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,34 +1353,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453779</v>
+        <v>453767</v>
       </c>
       <c r="R8" t="n">
-        <v>6991289</v>
+        <v>6991316</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,21 +1410,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1408,31 +1423,16 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756713</v>
+        <v>124756712</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91410</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124756711</v>
+        <v>124756714</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453779</v>
+        <v>453714</v>
       </c>
       <c r="R5" t="n">
-        <v>6991289</v>
+        <v>6991389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,21 +1082,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124756714</v>
+        <v>124756711</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453714</v>
+        <v>453779</v>
       </c>
       <c r="R6" t="n">
-        <v>6991389</v>
+        <v>6991289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,6 +1194,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1230,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124756712</v>
+        <v>124753575</v>
       </c>
       <c r="B7" t="n">
-        <v>91410</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,29 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453753</v>
+        <v>453767</v>
       </c>
       <c r="R7" t="n">
-        <v>6991387</v>
+        <v>6991316</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,19 +1298,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,19 +1315,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124753575</v>
+        <v>124756713</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1373,14 +1363,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453767</v>
+        <v>453753</v>
       </c>
       <c r="R8" t="n">
-        <v>6991316</v>
+        <v>6991387</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,9 +1400,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,12 +1427,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124709483</v>
+        <v>124709059</v>
       </c>
       <c r="B2" t="n">
-        <v>91579</v>
+        <v>74824</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>1460</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453754</v>
+        <v>453778</v>
       </c>
       <c r="R2" t="n">
-        <v>6991313</v>
+        <v>6991352</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124709059</v>
+        <v>124709483</v>
       </c>
       <c r="B3" t="n">
-        <v>74824</v>
+        <v>91579</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1460</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453778</v>
+        <v>453754</v>
       </c>
       <c r="R3" t="n">
-        <v>6991352</v>
+        <v>6991313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756712</v>
+        <v>124756711</v>
       </c>
       <c r="B4" t="n">
-        <v>91410</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,16 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453753</v>
+        <v>453779</v>
       </c>
       <c r="R4" t="n">
-        <v>6991387</v>
+        <v>6991289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,6 +975,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -986,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124756714</v>
+        <v>124753575</v>
       </c>
       <c r="B5" t="n">
         <v>91012</v>
@@ -1022,14 +1042,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453714</v>
+        <v>453767</v>
       </c>
       <c r="R5" t="n">
-        <v>6991389</v>
+        <v>6991316</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,19 +1079,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124756711</v>
+        <v>124756713</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453779</v>
+        <v>453753</v>
       </c>
       <c r="R6" t="n">
-        <v>6991289</v>
+        <v>6991387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,21 +1204,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1225,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124753575</v>
+        <v>124756712</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,34 +1236,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453767</v>
+        <v>453753</v>
       </c>
       <c r="R7" t="n">
-        <v>6991316</v>
+        <v>6991387</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,9 +1288,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,19 +1315,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124756713</v>
+        <v>124756714</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453753</v>
+        <v>453714</v>
       </c>
       <c r="R8" t="n">
-        <v>6991387</v>
+        <v>6991389</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124709059</v>
+        <v>124709483</v>
       </c>
       <c r="B2" t="n">
-        <v>74824</v>
+        <v>91579</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1460</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453778</v>
+        <v>453754</v>
       </c>
       <c r="R2" t="n">
-        <v>6991352</v>
+        <v>6991313</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124709483</v>
+        <v>124709059</v>
       </c>
       <c r="B3" t="n">
-        <v>91579</v>
+        <v>74824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>1460</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453754</v>
+        <v>453778</v>
       </c>
       <c r="R3" t="n">
-        <v>6991313</v>
+        <v>6991352</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756711</v>
+        <v>124756713</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453779</v>
+        <v>453753</v>
       </c>
       <c r="R4" t="n">
-        <v>6991289</v>
+        <v>6991387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,21 +975,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124753575</v>
+        <v>124756714</v>
       </c>
       <c r="B5" t="n">
         <v>91012</v>
@@ -1042,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453767</v>
+        <v>453714</v>
       </c>
       <c r="R5" t="n">
-        <v>6991316</v>
+        <v>6991389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,9 +1064,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124756713</v>
+        <v>124756712</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91410</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1119,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1220,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124756712</v>
+        <v>124756711</v>
       </c>
       <c r="B7" t="n">
-        <v>91410</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,16 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453753</v>
+        <v>453779</v>
       </c>
       <c r="R7" t="n">
-        <v>6991387</v>
+        <v>6991289</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,6 +1306,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1327,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124756714</v>
+        <v>124753575</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1363,14 +1373,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453714</v>
+        <v>453767</v>
       </c>
       <c r="R8" t="n">
-        <v>6991389</v>
+        <v>6991316</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,19 +1410,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,12 +1427,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756713</v>
+        <v>124756714</v>
       </c>
       <c r="B4" t="n">
         <v>91012</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453753</v>
+        <v>453714</v>
       </c>
       <c r="R4" t="n">
-        <v>6991387</v>
+        <v>6991389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124756714</v>
+        <v>124753575</v>
       </c>
       <c r="B5" t="n">
         <v>91012</v>
@@ -1027,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453714</v>
+        <v>453767</v>
       </c>
       <c r="R5" t="n">
-        <v>6991389</v>
+        <v>6991316</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,19 +1064,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,12 +1081,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1337,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124753575</v>
+        <v>124756713</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1373,14 +1363,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453767</v>
+        <v>453753</v>
       </c>
       <c r="R8" t="n">
-        <v>6991316</v>
+        <v>6991387</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,9 +1400,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,12 +1427,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124709483</v>
+        <v>124709059</v>
       </c>
       <c r="B2" t="n">
-        <v>91579</v>
+        <v>74824</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>1460</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453754</v>
+        <v>453778</v>
       </c>
       <c r="R2" t="n">
-        <v>6991313</v>
+        <v>6991352</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124709059</v>
+        <v>124709483</v>
       </c>
       <c r="B3" t="n">
-        <v>74824</v>
+        <v>91579</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1460</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453778</v>
+        <v>453754</v>
       </c>
       <c r="R3" t="n">
-        <v>6991352</v>
+        <v>6991313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756714</v>
+        <v>124756711</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453714</v>
+        <v>453779</v>
       </c>
       <c r="R4" t="n">
-        <v>6991389</v>
+        <v>6991289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,6 +975,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -991,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124753575</v>
+        <v>124756713</v>
       </c>
       <c r="B5" t="n">
         <v>91012</v>
@@ -1027,14 +1042,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453767</v>
+        <v>453753</v>
       </c>
       <c r="R5" t="n">
-        <v>6991316</v>
+        <v>6991387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,9 +1079,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,12 +1106,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1200,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124756711</v>
+        <v>124753575</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,34 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453779</v>
+        <v>453767</v>
       </c>
       <c r="R7" t="n">
-        <v>6991289</v>
+        <v>6991316</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,21 +1298,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1296,38 +1311,23 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124756713</v>
+        <v>124756714</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453753</v>
+        <v>453714</v>
       </c>
       <c r="R8" t="n">
-        <v>6991387</v>
+        <v>6991389</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756711</v>
+        <v>124756712</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91410</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453779</v>
+        <v>453753</v>
       </c>
       <c r="R4" t="n">
-        <v>6991289</v>
+        <v>6991387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,21 +970,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124756713</v>
+        <v>124756711</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453753</v>
+        <v>453779</v>
       </c>
       <c r="R5" t="n">
-        <v>6991387</v>
+        <v>6991289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,6 +1082,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124756712</v>
+        <v>124756714</v>
       </c>
       <c r="B6" t="n">
-        <v>91410</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,16 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453753</v>
+        <v>453714</v>
       </c>
       <c r="R6" t="n">
-        <v>6991387</v>
+        <v>6991389</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124753575</v>
+        <v>124756713</v>
       </c>
       <c r="B7" t="n">
         <v>91012</v>
@@ -1261,14 +1261,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453767</v>
+        <v>453753</v>
       </c>
       <c r="R7" t="n">
-        <v>6991316</v>
+        <v>6991387</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,9 +1298,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,19 +1325,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124756714</v>
+        <v>124753575</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1363,14 +1373,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453714</v>
+        <v>453767</v>
       </c>
       <c r="R8" t="n">
-        <v>6991389</v>
+        <v>6991316</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,19 +1410,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,12 +1427,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756712</v>
+        <v>124756711</v>
       </c>
       <c r="B4" t="n">
-        <v>91410</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,16 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453753</v>
+        <v>453779</v>
       </c>
       <c r="R4" t="n">
-        <v>6991387</v>
+        <v>6991289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,6 +975,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -986,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124756711</v>
+        <v>124756714</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453779</v>
+        <v>453714</v>
       </c>
       <c r="R5" t="n">
-        <v>6991289</v>
+        <v>6991389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,21 +1102,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1113,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124756714</v>
+        <v>124756713</v>
       </c>
       <c r="B6" t="n">
         <v>91012</v>
@@ -1153,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453714</v>
+        <v>453753</v>
       </c>
       <c r="R6" t="n">
-        <v>6991389</v>
+        <v>6991387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124756713</v>
+        <v>124756712</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1246,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124709059</v>
+        <v>124709483</v>
       </c>
       <c r="B2" t="n">
-        <v>74824</v>
+        <v>91579</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1460</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453778</v>
+        <v>453754</v>
       </c>
       <c r="R2" t="n">
-        <v>6991352</v>
+        <v>6991313</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124709483</v>
+        <v>124709059</v>
       </c>
       <c r="B3" t="n">
-        <v>91579</v>
+        <v>74824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>1460</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453754</v>
+        <v>453778</v>
       </c>
       <c r="R3" t="n">
-        <v>6991313</v>
+        <v>6991352</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756711</v>
+        <v>124756714</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453779</v>
+        <v>453714</v>
       </c>
       <c r="R4" t="n">
-        <v>6991289</v>
+        <v>6991389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,21 +975,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124756714</v>
+        <v>124756712</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91410</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1007,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453714</v>
+        <v>453753</v>
       </c>
       <c r="R5" t="n">
-        <v>6991389</v>
+        <v>6991387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124756713</v>
+        <v>124756711</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453753</v>
+        <v>453779</v>
       </c>
       <c r="R6" t="n">
-        <v>6991387</v>
+        <v>6991289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,6 +1194,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1230,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124756712</v>
+        <v>124753575</v>
       </c>
       <c r="B7" t="n">
-        <v>91410</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,29 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453753</v>
+        <v>453767</v>
       </c>
       <c r="R7" t="n">
-        <v>6991387</v>
+        <v>6991316</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,19 +1298,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,19 +1315,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124753575</v>
+        <v>124756713</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1373,14 +1363,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453767</v>
+        <v>453753</v>
       </c>
       <c r="R8" t="n">
-        <v>6991316</v>
+        <v>6991387</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,9 +1400,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,12 +1427,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124709483</v>
+        <v>124709059</v>
       </c>
       <c r="B2" t="n">
-        <v>91579</v>
+        <v>74824</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>1460</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453754</v>
+        <v>453778</v>
       </c>
       <c r="R2" t="n">
-        <v>6991313</v>
+        <v>6991352</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124709059</v>
+        <v>124709483</v>
       </c>
       <c r="B3" t="n">
-        <v>74824</v>
+        <v>91579</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1460</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453778</v>
+        <v>453754</v>
       </c>
       <c r="R3" t="n">
-        <v>6991352</v>
+        <v>6991313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756714</v>
+        <v>124756711</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453714</v>
+        <v>453779</v>
       </c>
       <c r="R4" t="n">
-        <v>6991389</v>
+        <v>6991289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,6 +975,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1098,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124756711</v>
+        <v>124756714</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453779</v>
+        <v>453714</v>
       </c>
       <c r="R6" t="n">
-        <v>6991289</v>
+        <v>6991389</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,21 +1209,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1225,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124753575</v>
+        <v>124756713</v>
       </c>
       <c r="B7" t="n">
         <v>91012</v>
@@ -1261,14 +1261,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453767</v>
+        <v>453753</v>
       </c>
       <c r="R7" t="n">
-        <v>6991316</v>
+        <v>6991387</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,9 +1298,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,19 +1325,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124756713</v>
+        <v>124753575</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1363,14 +1373,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453753</v>
+        <v>453767</v>
       </c>
       <c r="R8" t="n">
-        <v>6991387</v>
+        <v>6991316</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,19 +1410,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,12 +1427,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756711</v>
+        <v>124756714</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453779</v>
+        <v>453714</v>
       </c>
       <c r="R4" t="n">
-        <v>6991289</v>
+        <v>6991389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,21 +975,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124756712</v>
+        <v>124756711</v>
       </c>
       <c r="B5" t="n">
-        <v>91410</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,16 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453753</v>
+        <v>453779</v>
       </c>
       <c r="R5" t="n">
-        <v>6991387</v>
+        <v>6991289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,6 +1087,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1113,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124756714</v>
+        <v>124756713</v>
       </c>
       <c r="B6" t="n">
         <v>91012</v>
@@ -1153,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453714</v>
+        <v>453753</v>
       </c>
       <c r="R6" t="n">
-        <v>6991389</v>
+        <v>6991387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124756713</v>
+        <v>124756712</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1246,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124709059</v>
       </c>
       <c r="B2" t="n">
-        <v>74824</v>
+        <v>74948</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>124709483</v>
       </c>
       <c r="B3" t="n">
-        <v>91579</v>
+        <v>91737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756714</v>
+        <v>124753575</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453714</v>
+        <v>453767</v>
       </c>
       <c r="R4" t="n">
-        <v>6991389</v>
+        <v>6991316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +952,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124756711</v>
+        <v>124756712</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>91570</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453779</v>
+        <v>453753</v>
       </c>
       <c r="R5" t="n">
-        <v>6991289</v>
+        <v>6991387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1051,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1061,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,21 +1072,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124756713</v>
+        <v>124756711</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453753</v>
+        <v>453779</v>
       </c>
       <c r="R6" t="n">
-        <v>6991387</v>
+        <v>6991289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,6 +1184,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1230,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124756712</v>
+        <v>124756713</v>
       </c>
       <c r="B7" t="n">
-        <v>91410</v>
+        <v>91166</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,16 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1337,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124753575</v>
+        <v>124756714</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,14 +1363,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453767</v>
+        <v>453714</v>
       </c>
       <c r="R8" t="n">
-        <v>6991316</v>
+        <v>6991389</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,9 +1400,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,12 +1427,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124753575</v>
+        <v>124756713</v>
       </c>
       <c r="B4" t="n">
         <v>91166</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453767</v>
+        <v>453753</v>
       </c>
       <c r="R4" t="n">
-        <v>6991316</v>
+        <v>6991387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,9 +952,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124756711</v>
+        <v>124756714</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453779</v>
+        <v>453714</v>
       </c>
       <c r="R6" t="n">
-        <v>6991289</v>
+        <v>6991389</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,21 +1194,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124756713</v>
+        <v>124756711</v>
       </c>
       <c r="B7" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453753</v>
+        <v>453779</v>
       </c>
       <c r="R7" t="n">
-        <v>6991387</v>
+        <v>6991289</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,6 +1306,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1327,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124756714</v>
+        <v>124753575</v>
       </c>
       <c r="B8" t="n">
         <v>91166</v>
@@ -1363,14 +1373,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453714</v>
+        <v>453767</v>
       </c>
       <c r="R8" t="n">
-        <v>6991389</v>
+        <v>6991316</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,19 +1410,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,12 +1427,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124709059</v>
+        <v>124709483</v>
       </c>
       <c r="B2" t="n">
-        <v>74948</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1460</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453778</v>
+        <v>453754</v>
       </c>
       <c r="R2" t="n">
-        <v>6991352</v>
+        <v>6991313</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124709483</v>
+        <v>124756710</v>
       </c>
       <c r="B3" t="n">
-        <v>91737</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453754</v>
+        <v>453806</v>
       </c>
       <c r="R3" t="n">
-        <v>6991313</v>
+        <v>6991340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,31 +863,41 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Klen torrgran i myrkant. # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124756713</v>
+        <v>124753575</v>
       </c>
       <c r="B4" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,14 +925,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453753</v>
+        <v>453767</v>
       </c>
       <c r="R4" t="n">
-        <v>6991387</v>
+        <v>6991316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,19 +962,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,27 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124756712</v>
+        <v>124756713</v>
       </c>
       <c r="B5" t="n">
-        <v>91570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,16 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1101,12 +1101,7 @@
         <v>124756714</v>
       </c>
       <c r="B6" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124756711</v>
+        <v>124709059</v>
       </c>
       <c r="B7" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjärnflon Ö, Jmt</t>
+          <t>Svarttjärnen, Svarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453779</v>
+        <v>453778</v>
       </c>
       <c r="R7" t="n">
-        <v>6991289</v>
+        <v>6991352</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,22 +1270,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,46 +1286,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124753575</v>
+        <v>124756711</v>
       </c>
       <c r="B8" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,34 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Häggsåsen N, Jmt</t>
+          <t>Tjärnflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453767</v>
+        <v>453779</v>
       </c>
       <c r="R8" t="n">
-        <v>6991316</v>
+        <v>6991289</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,11 +1370,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1423,19 +1393,141 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124756712</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tjärnflon Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>453753</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6991387</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12973-2024 artfynd.xlsx
+++ b/artfynd/A 12973-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124709483</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756710</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753575</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756713</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756714</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124709059</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756711</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,8 +1568,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756712</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>